--- a/BeatnotePostHotCell/Jun17,2026/Fit_ResultJun17.xlsx
+++ b/BeatnotePostHotCell/Jun17,2026/Fit_ResultJun17.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Wolfwalker\Documents\git\6s7p\BeatnotePostHotCell\Jun17,2026\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Diego\git\6s7p\BeatnotePostHotCell\Jun17,2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1FA8C14D-6056-420A-A4CB-6624687BA3AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D17E736-B643-4C63-9737-BABEC9746123}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" activeTab="2" xr2:uid="{D9E101C5-8284-4B59-8B1C-2AD2D5F2FDD3}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{D9E101C5-8284-4B59-8B1C-2AD2D5F2FDD3}"/>
   </bookViews>
   <sheets>
     <sheet name="894" sheetId="2" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="30">
   <si>
     <t>Date</t>
   </si>
@@ -129,19 +129,13 @@
   </si>
   <si>
     <t>Jun17,2026+12-46-56PM</t>
-  </si>
-  <si>
-    <t>Jun17,2026+10-47-10AM</t>
-  </si>
-  <si>
-    <t>Jun17,2026+9-59-16AM</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -513,9 +507,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{40C5617D-2BBC-4C21-ADC4-3687FEC8C6E3}">
   <dimension ref="A1:S33"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
-    <row r="1" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:19">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -551,7 +545,7 @@
       <c r="R1" s="1"/>
       <c r="S1" s="1"/>
     </row>
-    <row r="2" spans="1:19" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:19" ht="42.75">
       <c r="A2" s="1" t="s">
         <v>19</v>
       </c>
@@ -578,7 +572,7 @@
       <c r="R2" s="1"/>
       <c r="S2" s="1"/>
     </row>
-    <row r="3" spans="1:19" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:19" ht="42.75">
       <c r="A3" s="1" t="s">
         <v>20</v>
       </c>
@@ -604,7 +598,7 @@
       <c r="Q3" s="1"/>
       <c r="S3" s="1"/>
     </row>
-    <row r="4" spans="1:19" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:19" ht="42.75">
       <c r="A4" s="1" t="s">
         <v>11</v>
       </c>
@@ -630,7 +624,7 @@
       <c r="Q4" s="1"/>
       <c r="S4" s="1"/>
     </row>
-    <row r="5" spans="1:19" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:19" ht="42.75">
       <c r="A5" s="1" t="s">
         <v>12</v>
       </c>
@@ -656,7 +650,7 @@
       <c r="Q5" s="1"/>
       <c r="S5" s="1"/>
     </row>
-    <row r="6" spans="1:19" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:19" ht="42.75">
       <c r="A6" s="1" t="s">
         <v>13</v>
       </c>
@@ -688,7 +682,7 @@
       <c r="Q6" s="1"/>
       <c r="S6" s="1"/>
     </row>
-    <row r="7" spans="1:19" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:19" ht="42.75">
       <c r="A7" s="1" t="s">
         <v>14</v>
       </c>
@@ -713,7 +707,7 @@
       <c r="Q7" s="1"/>
       <c r="S7" s="1"/>
     </row>
-    <row r="8" spans="1:19" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:19" ht="42.75">
       <c r="A8" s="1" t="s">
         <v>15</v>
       </c>
@@ -738,7 +732,7 @@
       <c r="Q8" s="1"/>
       <c r="S8" s="1"/>
     </row>
-    <row r="9" spans="1:19" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:19" ht="42.75">
       <c r="A9" s="1" t="s">
         <v>16</v>
       </c>
@@ -763,7 +757,7 @@
       <c r="Q9" s="1"/>
       <c r="S9" s="1"/>
     </row>
-    <row r="10" spans="1:19" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:19" ht="42.75">
       <c r="A10" s="1" t="s">
         <v>17</v>
       </c>
@@ -788,7 +782,7 @@
       <c r="Q10" s="1"/>
       <c r="S10" s="1"/>
     </row>
-    <row r="11" spans="1:19" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:19" ht="42.75">
       <c r="A11" s="1" t="s">
         <v>18</v>
       </c>
@@ -813,7 +807,7 @@
       <c r="Q11" s="1"/>
       <c r="R11" s="1"/>
     </row>
-    <row r="12" spans="1:19" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:19" ht="42.75">
       <c r="A12" s="1" t="s">
         <v>24</v>
       </c>
@@ -837,7 +831,7 @@
       </c>
       <c r="R12" s="1"/>
     </row>
-    <row r="13" spans="1:19" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:19" ht="42.75">
       <c r="A13" s="1" t="s">
         <v>25</v>
       </c>
@@ -861,7 +855,7 @@
       </c>
       <c r="R13" s="1"/>
     </row>
-    <row r="14" spans="1:19" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:19" ht="42.75">
       <c r="A14" s="1" t="s">
         <v>26</v>
       </c>
@@ -885,7 +879,7 @@
       </c>
       <c r="R14" s="1"/>
     </row>
-    <row r="15" spans="1:19" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:19" ht="42.75">
       <c r="A15" s="1" t="s">
         <v>27</v>
       </c>
@@ -909,7 +903,7 @@
       </c>
       <c r="R15" s="1"/>
     </row>
-    <row r="16" spans="1:19" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:19" ht="42.75">
       <c r="A16" s="1" t="s">
         <v>28</v>
       </c>
@@ -934,7 +928,7 @@
       <c r="H16" s="1"/>
       <c r="R16" s="1"/>
     </row>
-    <row r="17" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:8" ht="42.75">
       <c r="A17" s="1" t="s">
         <v>29</v>
       </c>
@@ -958,7 +952,7 @@
       </c>
       <c r="H17" s="1"/>
     </row>
-    <row r="18" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:8" ht="42.75">
       <c r="A18" s="1" t="s">
         <v>21</v>
       </c>
@@ -982,7 +976,7 @@
       </c>
       <c r="H18" s="1"/>
     </row>
-    <row r="19" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:8" ht="42.75">
       <c r="A19" s="1" t="s">
         <v>22</v>
       </c>
@@ -1006,7 +1000,7 @@
       </c>
       <c r="H19" s="1"/>
     </row>
-    <row r="20" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:8" ht="42.75">
       <c r="A20" s="1" t="s">
         <v>23</v>
       </c>
@@ -1030,7 +1024,7 @@
       </c>
       <c r="H20" s="1"/>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:8">
       <c r="A21" s="1"/>
       <c r="B21" s="1"/>
       <c r="C21" s="1"/>
@@ -1040,7 +1034,7 @@
       <c r="G21" s="1"/>
       <c r="H21" s="1"/>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:8">
       <c r="A22" s="1"/>
       <c r="B22" s="1"/>
       <c r="C22" s="1"/>
@@ -1049,7 +1043,7 @@
       <c r="F22" s="1"/>
       <c r="G22" s="1"/>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:8">
       <c r="A23" s="1"/>
       <c r="B23" s="1"/>
       <c r="C23" s="1"/>
@@ -1058,7 +1052,7 @@
       <c r="F23" s="1"/>
       <c r="G23" s="1"/>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:8">
       <c r="A24" s="1"/>
       <c r="B24" s="1"/>
       <c r="C24" s="1"/>
@@ -1067,7 +1061,7 @@
       <c r="F24" s="1"/>
       <c r="G24" s="1"/>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:8">
       <c r="A25" s="1"/>
       <c r="B25" s="1"/>
       <c r="C25" s="1"/>
@@ -1076,7 +1070,7 @@
       <c r="F25" s="1"/>
       <c r="G25" s="1"/>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:8">
       <c r="A26" s="1"/>
       <c r="B26" s="1"/>
       <c r="C26" s="1"/>
@@ -1085,7 +1079,7 @@
       <c r="F26" s="1"/>
       <c r="G26" s="1"/>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:8">
       <c r="A27" s="1"/>
       <c r="B27" s="1"/>
       <c r="C27" s="1"/>
@@ -1094,7 +1088,7 @@
       <c r="F27" s="1"/>
       <c r="G27" s="1"/>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:8">
       <c r="A28" s="1"/>
       <c r="B28" s="1"/>
       <c r="C28" s="1"/>
@@ -1103,7 +1097,7 @@
       <c r="F28" s="1"/>
       <c r="G28" s="1"/>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:8">
       <c r="A29" s="1"/>
       <c r="B29" s="1"/>
       <c r="C29" s="1"/>
@@ -1112,7 +1106,7 @@
       <c r="F29" s="1"/>
       <c r="G29" s="1"/>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:8">
       <c r="A30" s="1"/>
       <c r="B30" s="1"/>
       <c r="C30" s="1"/>
@@ -1121,7 +1115,7 @@
       <c r="F30" s="1"/>
       <c r="G30" s="1"/>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:8">
       <c r="A31" s="1"/>
       <c r="B31" s="1"/>
       <c r="C31" s="1"/>
@@ -1130,7 +1124,7 @@
       <c r="F31" s="1"/>
       <c r="G31" s="1"/>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:8">
       <c r="A32" s="1"/>
       <c r="B32" s="1"/>
       <c r="C32" s="1"/>
@@ -1139,7 +1133,7 @@
       <c r="F32" s="1"/>
       <c r="G32" s="1"/>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:7">
       <c r="A33" s="1"/>
       <c r="B33" s="1"/>
       <c r="C33" s="1"/>
@@ -1155,10 +1149,10 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{011646E0-737D-49FA-A2CA-7848F848076B}">
-  <dimension ref="A1:T40"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:T39"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
-    <row r="1" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:20">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1185,37 +1179,21 @@
       </c>
       <c r="I1" s="1"/>
       <c r="L1" s="1"/>
-      <c r="M1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="P1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="Q1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="R1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="S1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="T1" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="2" spans="1:20" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="M1" s="1"/>
+      <c r="N1" s="1"/>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+      <c r="T1" s="1"/>
+    </row>
+    <row r="2" spans="1:20" ht="42.75">
       <c r="A2" s="1" t="s">
         <v>19</v>
       </c>
       <c r="B2" s="1">
-        <v>0.17294771128421699</v>
+        <v>0.13468054835968099</v>
       </c>
       <c r="C2" s="1">
         <v>1.5258946188107001</v>
@@ -1227,22 +1205,21 @@
         <v>-2.4115279182887399E-4</v>
       </c>
       <c r="F2" s="1">
-        <v>3.4728580337975701</v>
+        <v>3.41163937067796</v>
       </c>
       <c r="G2" s="1">
-        <v>39.603619218171801</v>
+        <v>39.586670815866903</v>
       </c>
       <c r="H2" s="1">
-        <v>7.2853941162822602E-4</v>
-      </c>
-      <c r="L2" s="1"/>
-    </row>
-    <row r="3" spans="1:20" ht="43.5" x14ac:dyDescent="0.35">
+        <v>6.39285007169414E-4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:20" ht="42.75">
       <c r="A3" s="1" t="s">
         <v>20</v>
       </c>
       <c r="B3" s="1">
-        <v>0.175665485735155</v>
+        <v>0.13679830071593899</v>
       </c>
       <c r="C3" s="1">
         <v>1.52602927616929</v>
@@ -1254,549 +1231,516 @@
         <v>-1.60134972587651E-4</v>
       </c>
       <c r="F3" s="1">
-        <v>3.4809228345394998</v>
+        <v>3.4197315320633002</v>
       </c>
       <c r="G3" s="1">
-        <v>41.599934119955698</v>
+        <v>41.575314978279899</v>
       </c>
       <c r="H3" s="1">
-        <v>1.15229823951594E-3</v>
-      </c>
-      <c r="L3" s="1"/>
-    </row>
-    <row r="4" spans="1:20" ht="43.5" x14ac:dyDescent="0.35">
+        <v>1.0583695165581599E-3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:20" ht="42.75">
       <c r="A4" s="1" t="s">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="B4" s="1">
-        <v>0.17351834771128199</v>
+        <v>0.135403359867214</v>
       </c>
       <c r="C4" s="1">
-        <v>1.5264782997959701</v>
+        <v>1.5266411905308599</v>
       </c>
       <c r="D4" s="1">
-        <v>2.10962357084907E-3</v>
+        <v>2.0861805235716799E-3</v>
       </c>
       <c r="E4" s="1">
-        <v>-1.2315329262803799E-4</v>
+        <v>-1.2890988211342801E-4</v>
       </c>
       <c r="F4" s="1">
-        <v>3.47230704551309</v>
+        <v>3.4140908424579401</v>
       </c>
       <c r="G4" s="1">
-        <v>39.814207589544701</v>
+        <v>41.458418552088901</v>
       </c>
       <c r="H4" s="1">
-        <v>5.84829964132661E-4</v>
-      </c>
-    </row>
-    <row r="5" spans="1:20" ht="43.5" x14ac:dyDescent="0.35">
+        <v>1.06399189160318E-3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:20" ht="42.75">
       <c r="A5" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B5" s="1">
-        <v>0.17382778027635701</v>
+        <v>0.13595989010586099</v>
       </c>
       <c r="C5" s="1">
-        <v>1.5266411905308599</v>
+        <v>1.5268369959289501</v>
       </c>
       <c r="D5" s="1">
-        <v>2.0861805235716799E-3</v>
+        <v>2.5359298199264298E-3</v>
       </c>
       <c r="E5" s="1">
-        <v>-1.2890988211342801E-4</v>
+        <v>-2.09034019083978E-4</v>
       </c>
       <c r="F5" s="1">
-        <v>3.4752832307887198</v>
+        <v>3.1672101937680899</v>
       </c>
       <c r="G5" s="1">
-        <v>41.674322587351398</v>
+        <v>41.6523403223663</v>
       </c>
       <c r="H5" s="1">
-        <v>9.1343413226320296E-4</v>
-      </c>
-    </row>
-    <row r="6" spans="1:20" ht="43.5" x14ac:dyDescent="0.35">
+        <v>1.1527678748615099E-3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:20" ht="42.75">
       <c r="A6" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B6" s="1">
-        <v>0.17455983570099701</v>
+        <v>0.13748020113746301</v>
       </c>
       <c r="C6" s="1">
-        <v>1.5268369959289501</v>
+        <v>1.5271863000813699</v>
       </c>
       <c r="D6" s="1">
-        <v>2.5359298199264298E-3</v>
-      </c>
-      <c r="E6" s="1">
-        <v>-2.09034019083978E-4</v>
+        <v>1.7459168478455201E-3</v>
+      </c>
+      <c r="E6" s="2">
+        <v>-9.5800377484653898E-5</v>
       </c>
       <c r="F6" s="1">
-        <v>3.22839340597214</v>
+        <v>3.1636543603796801</v>
       </c>
       <c r="G6" s="1">
-        <v>41.661538184660699</v>
+        <v>41.082653966299603</v>
       </c>
       <c r="H6" s="1">
-        <v>1.1443235717986599E-3</v>
-      </c>
-    </row>
-    <row r="7" spans="1:20" ht="43.5" x14ac:dyDescent="0.35">
+        <v>5.8453176327384203E-4</v>
+      </c>
+      <c r="I6" s="1"/>
+      <c r="J6" s="1"/>
+      <c r="K6" s="1"/>
+      <c r="L6" s="1"/>
+      <c r="M6" s="1"/>
+      <c r="N6" s="1"/>
+      <c r="O6" s="1"/>
+      <c r="P6" s="1"/>
+    </row>
+    <row r="7" spans="1:20" ht="42.75">
       <c r="A7" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B7" s="1">
-        <v>0.17664296551393399</v>
+        <v>0.13777383840185101</v>
       </c>
       <c r="C7" s="1">
-        <v>1.52707599137846</v>
+        <v>1.52571235644967</v>
       </c>
       <c r="D7" s="1">
-        <v>1.8481463977159699E-3</v>
+        <v>2.23413251859347E-3</v>
       </c>
       <c r="E7" s="1">
-        <v>-1.11152690654579E-4</v>
+        <v>-1.43621690244121E-4</v>
       </c>
       <c r="F7" s="1">
-        <v>3.22483372112002</v>
+        <v>3.1603296839085702</v>
       </c>
       <c r="G7" s="1">
-        <v>41.677466946461699</v>
+        <v>40.722015157647803</v>
       </c>
       <c r="H7" s="1">
-        <v>5.7927305713437204E-4</v>
-      </c>
-      <c r="I7" s="1"/>
-      <c r="J7" s="1"/>
-      <c r="K7" s="1"/>
-      <c r="L7" s="1"/>
-      <c r="M7" s="1"/>
-      <c r="N7" s="1"/>
-      <c r="O7" s="1"/>
-      <c r="P7" s="1"/>
-    </row>
-    <row r="8" spans="1:20" ht="43.5" x14ac:dyDescent="0.35">
+        <v>7.5218433847388697E-4</v>
+      </c>
+    </row>
+    <row r="8" spans="1:20" ht="42.75">
       <c r="A8" s="1" t="s">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="B8" s="1">
-        <v>0.17911658675275099</v>
+        <v>0.13676101673190699</v>
       </c>
       <c r="C8" s="1">
-        <v>1.52590312302192</v>
+        <v>1.5256031612350001</v>
       </c>
       <c r="D8" s="1">
-        <v>2.1405898338959302E-3</v>
+        <v>2.3423075315198499E-3</v>
       </c>
       <c r="E8" s="1">
-        <v>-1.3373961353737001E-4</v>
+        <v>-1.3136327272120999E-4</v>
       </c>
       <c r="F8" s="1">
-        <v>3.2316196338260301</v>
+        <v>3.1643411341296801</v>
       </c>
       <c r="G8" s="1">
-        <v>41.294608344140798</v>
+        <v>39.7132780634985</v>
       </c>
       <c r="H8" s="1">
-        <v>7.7386612138828496E-4</v>
-      </c>
-    </row>
-    <row r="9" spans="1:20" ht="43.5" x14ac:dyDescent="0.35">
+        <v>6.5953156652746902E-4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:20" ht="42.75">
       <c r="A9" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B9" s="1">
-        <v>0.17708531560420199</v>
+        <v>0.13512046849112699</v>
       </c>
       <c r="C9" s="1">
-        <v>1.52571235644967</v>
+        <v>1.52582073829446</v>
       </c>
       <c r="D9" s="1">
-        <v>2.23413251859347E-3</v>
+        <v>2.5957042856930698E-3</v>
       </c>
       <c r="E9" s="1">
-        <v>-1.43621690244121E-4</v>
+        <v>-1.8167299551369499E-4</v>
       </c>
       <c r="F9" s="1">
-        <v>3.221533088288</v>
+        <v>3.1680176061674401</v>
       </c>
       <c r="G9" s="1">
-        <v>41.640814088544403</v>
+        <v>39.754992045839103</v>
       </c>
       <c r="H9" s="1">
-        <v>1.03044844816607E-3</v>
-      </c>
-    </row>
-    <row r="10" spans="1:20" ht="43.5" x14ac:dyDescent="0.35">
+        <v>6.6655643420864203E-4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:20" ht="42.75">
       <c r="A10" s="1" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B10" s="1">
-        <v>0.17557573140333699</v>
+        <v>0.13660109283925101</v>
       </c>
       <c r="C10" s="1">
-        <v>1.5256031612350001</v>
+        <v>1.52604552063201</v>
       </c>
       <c r="D10" s="1">
-        <v>2.3423075315198499E-3</v>
+        <v>2.4082386211540098E-3</v>
       </c>
       <c r="E10" s="1">
-        <v>-1.3136327272120999E-4</v>
+        <v>-1.6246359114856199E-4</v>
       </c>
       <c r="F10" s="1">
-        <v>3.2255389534595502</v>
+        <v>3.1706305253981899</v>
       </c>
       <c r="G10" s="1">
-        <v>39.791522638672198</v>
+        <v>41.463779605775102</v>
       </c>
       <c r="H10" s="1">
-        <v>5.7858075038553895E-4</v>
-      </c>
-    </row>
-    <row r="11" spans="1:20" ht="43.5" x14ac:dyDescent="0.35">
+        <v>1.1559480451092299E-3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:20" ht="42.75">
       <c r="A11" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B11" s="1">
-        <v>0.173457649972002</v>
+        <v>0.13641311645492901</v>
       </c>
       <c r="C11" s="1">
-        <v>1.52582073829446</v>
+        <v>1.5255164701892101</v>
       </c>
       <c r="D11" s="1">
-        <v>2.5957042856930698E-3</v>
+        <v>2.4968128386419499E-3</v>
       </c>
       <c r="E11" s="1">
-        <v>-1.8167299551369499E-4</v>
+        <v>-1.3772696124573399E-4</v>
       </c>
       <c r="F11" s="1">
-        <v>3.2292310330669598</v>
+        <v>3.4242839417525102</v>
       </c>
       <c r="G11" s="1">
-        <v>39.737276692617399</v>
+        <v>39.8743116711006</v>
       </c>
       <c r="H11" s="1">
-        <v>5.7859237366109898E-4</v>
-      </c>
-    </row>
-    <row r="12" spans="1:20" ht="43.5" x14ac:dyDescent="0.35">
+        <v>9.3746804188119795E-4</v>
+      </c>
+    </row>
+    <row r="12" spans="1:20" ht="42.75">
       <c r="A12" s="1" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="B12" s="1">
-        <v>0.17535865105134299</v>
+        <v>0.13599421764432501</v>
       </c>
       <c r="C12" s="1">
-        <v>1.52604552063201</v>
+        <v>1.5264746872922701</v>
       </c>
       <c r="D12" s="1">
-        <v>2.4082386211540098E-3</v>
+        <v>2.2733683994961402E-3</v>
       </c>
       <c r="E12" s="1">
-        <v>-1.6246359114856199E-4</v>
+        <v>-1.3267253122294101E-4</v>
       </c>
       <c r="F12" s="1">
-        <v>3.2318057917797298</v>
+        <v>2.91316450774965</v>
       </c>
       <c r="G12" s="1">
-        <v>41.532831749555797</v>
+        <v>41.8146179198067</v>
       </c>
       <c r="H12" s="1">
-        <v>1.0438110291910599E-3</v>
-      </c>
-    </row>
-    <row r="13" spans="1:20" ht="43.5" x14ac:dyDescent="0.35">
+        <v>1.1571538684543401E-3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:20" ht="42.75">
       <c r="A13" s="1" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="B13" s="1">
-        <v>0.175039518424147</v>
+        <v>0.133813897334362</v>
       </c>
       <c r="C13" s="1">
-        <v>1.5255164701892101</v>
+        <v>1.5246614334694599</v>
       </c>
       <c r="D13" s="1">
-        <v>2.4968128386419499E-3</v>
+        <v>2.9341721304828798E-3</v>
       </c>
       <c r="E13" s="1">
-        <v>-1.3772696124573399E-4</v>
+        <v>-1.92655797968772E-4</v>
       </c>
       <c r="F13" s="1">
-        <v>3.4854549626467901</v>
+        <v>3.1693340271333001</v>
       </c>
       <c r="G13" s="1">
-        <v>39.874060508218598</v>
+        <v>39.818111341098799</v>
       </c>
       <c r="H13" s="1">
-        <v>5.8354202997727895E-4</v>
-      </c>
-    </row>
-    <row r="14" spans="1:20" ht="43.5" x14ac:dyDescent="0.35">
+        <v>6.9801158091737595E-4</v>
+      </c>
+    </row>
+    <row r="14" spans="1:20" ht="42.75">
       <c r="A14" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B14" s="1">
-        <v>0.17459939950666101</v>
+        <v>0.13398818137368401</v>
       </c>
       <c r="C14" s="1">
-        <v>1.5264746872922701</v>
+        <v>1.5286682224238599</v>
       </c>
       <c r="D14" s="1">
-        <v>2.2733683994961402E-3</v>
+        <v>1.9529242764353401E-3</v>
       </c>
       <c r="E14" s="1">
-        <v>-1.3267253122294101E-4</v>
+        <v>-1.07462871268083E-4</v>
       </c>
       <c r="F14" s="1">
-        <v>2.97437144919859</v>
+        <v>1.12552361145562</v>
       </c>
       <c r="G14" s="1">
-        <v>41.814617919619302</v>
+        <v>39.798684605935001</v>
       </c>
       <c r="H14" s="1">
-        <v>1.1571538680334901E-3</v>
-      </c>
-    </row>
-    <row r="15" spans="1:20" ht="43.5" x14ac:dyDescent="0.35">
+        <v>5.8121351688101501E-4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:20" ht="42.75">
       <c r="A15" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B15" s="1">
-        <v>0.17177387798819599</v>
+        <v>0.135526162232535</v>
       </c>
       <c r="C15" s="1">
-        <v>1.5246614334694599</v>
+        <v>1.5253155021584399</v>
       </c>
       <c r="D15" s="1">
-        <v>2.9341721304828798E-3</v>
+        <v>2.6265717017228802E-3</v>
       </c>
       <c r="E15" s="1">
-        <v>-1.92655797968772E-4</v>
+        <v>-1.66094854505413E-4</v>
       </c>
       <c r="F15" s="1">
-        <v>3.2305514276304002</v>
+        <v>2.87761083305119</v>
       </c>
       <c r="G15" s="1">
-        <v>39.777724051620403</v>
+        <v>39.978398323225903</v>
       </c>
       <c r="H15" s="1">
-        <v>6.1154526635159097E-4</v>
-      </c>
-    </row>
-    <row r="16" spans="1:20" ht="43.5" x14ac:dyDescent="0.35">
+        <v>8.7169746412800399E-4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:20" ht="42.75">
       <c r="A16" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B16" s="1">
-        <v>0.172049396498035</v>
+        <v>0.13583799718759201</v>
       </c>
       <c r="C16" s="1">
-        <v>1.5286682224238599</v>
+        <v>1.5235696375414101</v>
       </c>
       <c r="D16" s="1">
-        <v>1.9529242764353401E-3</v>
+        <v>2.7538466370875801E-3</v>
       </c>
       <c r="E16" s="1">
-        <v>-1.07462871268083E-4</v>
+        <v>-1.4187323315291599E-4</v>
       </c>
       <c r="F16" s="1">
-        <v>1.18672795132277</v>
+        <v>3.1646472776399901</v>
       </c>
       <c r="G16" s="1">
-        <v>39.794145578950399</v>
+        <v>39.962922634377001</v>
       </c>
       <c r="H16" s="1">
-        <v>6.4681620991665202E-4</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
+        <v>8.7506037834080203E-4</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" ht="42.75">
       <c r="A17" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B17" s="1">
-        <v>0.17416028353340501</v>
+        <v>0.13529790524896701</v>
       </c>
       <c r="C17" s="1">
-        <v>1.5253155021584399</v>
+        <v>1.52270249893995</v>
       </c>
       <c r="D17" s="1">
-        <v>2.6265717017228802E-3</v>
+        <v>2.6600085455945502E-3</v>
       </c>
       <c r="E17" s="1">
-        <v>-1.66094854505413E-4</v>
+        <v>-1.3186491392954799E-4</v>
       </c>
       <c r="F17" s="1">
-        <v>2.9388204893912202</v>
+        <v>3.1702019307796698</v>
       </c>
       <c r="G17" s="1">
-        <v>40.5729767212759</v>
+        <v>39.831718847975999</v>
       </c>
       <c r="H17" s="1">
-        <v>1.15673502027382E-3</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
+        <v>5.7857736766886501E-4</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" ht="42.75">
       <c r="A18" s="1" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="B18" s="1">
-        <v>0.17432866559164001</v>
+        <v>0.13334859062780199</v>
       </c>
       <c r="C18" s="1">
-        <v>1.5235696375414101</v>
+        <v>1.52297113854633</v>
       </c>
       <c r="D18" s="1">
-        <v>2.7538466370875801E-3</v>
+        <v>2.8402938359539799E-3</v>
       </c>
       <c r="E18" s="1">
-        <v>-1.4187323315291599E-4</v>
+        <v>-1.9399700055577199E-4</v>
       </c>
       <c r="F18" s="1">
-        <v>3.22583424219268</v>
+        <v>2.6643958553320899</v>
       </c>
       <c r="G18" s="1">
-        <v>39.958510039538602</v>
+        <v>39.871203120065303</v>
       </c>
       <c r="H18" s="1">
-        <v>6.1984994197235202E-4</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
+        <v>5.7958846604316404E-4</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" ht="42.75">
       <c r="A19" s="1" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="B19" s="1">
-        <v>0.17371638201273101</v>
+        <v>0.13491725008311001</v>
       </c>
       <c r="C19" s="1">
-        <v>1.52270249893995</v>
+        <v>1.5246824653037701</v>
       </c>
       <c r="D19" s="1">
-        <v>2.6600085455945502E-3</v>
+        <v>2.74508792314837E-3</v>
       </c>
       <c r="E19" s="1">
-        <v>-1.3186491392954799E-4</v>
+        <v>-1.7385320046513201E-4</v>
       </c>
       <c r="F19" s="1">
-        <v>3.2314005443395502</v>
+        <v>2.6692399831684499</v>
       </c>
       <c r="G19" s="1">
-        <v>39.831717800921901</v>
+        <v>39.913198280465501</v>
       </c>
       <c r="H19" s="1">
-        <v>5.7865793714870998E-4</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
+        <v>7.7137459936806702E-4</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" ht="42.75">
       <c r="A20" s="1" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B20" s="1">
-        <v>0.17123203171632401</v>
+        <v>0.137631619653904</v>
       </c>
       <c r="C20" s="1">
-        <v>1.52297113854633</v>
+        <v>1.52402119569984</v>
       </c>
       <c r="D20" s="1">
-        <v>2.8402938359539799E-3</v>
+        <v>2.93125722269775E-3</v>
       </c>
       <c r="E20" s="1">
-        <v>-1.9399700055577199E-4</v>
+        <v>-1.8042694952051999E-4</v>
       </c>
       <c r="F20" s="1">
-        <v>2.7255773262060798</v>
+        <v>2.6732489288340999</v>
       </c>
       <c r="G20" s="1">
-        <v>39.871176595446798</v>
+        <v>39.930745511255203</v>
       </c>
       <c r="H20" s="1">
-        <v>6.5253224888675598E-4</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A21" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="B21" s="1">
-        <v>0.17318569822136001</v>
-      </c>
-      <c r="C21" s="1">
-        <v>1.5246824653037701</v>
-      </c>
-      <c r="D21" s="1">
-        <v>2.74508792314837E-3</v>
-      </c>
-      <c r="E21" s="1">
-        <v>-1.7385320046513201E-4</v>
-      </c>
-      <c r="F21" s="1">
-        <v>2.7304507263117501</v>
-      </c>
-      <c r="G21" s="1">
-        <v>39.975526733816402</v>
-      </c>
-      <c r="H21" s="1">
-        <v>6.2448431112533103E-4</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A22" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="B22" s="1">
-        <v>0.17669669700448201</v>
-      </c>
-      <c r="C22" s="1">
-        <v>1.52402119569984</v>
-      </c>
-      <c r="D22" s="1">
-        <v>2.93125722269775E-3</v>
-      </c>
-      <c r="E22" s="1">
-        <v>-1.8042694952051999E-4</v>
-      </c>
-      <c r="F22" s="1">
-        <v>2.7344301249166398</v>
-      </c>
-      <c r="G22" s="1">
-        <v>39.993956579034297</v>
-      </c>
-      <c r="H22" s="1">
-        <v>5.8045058441543004E-4</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.35">
+        <v>6.4734249431275205E-4</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8">
+      <c r="A21" s="1"/>
+      <c r="B21" s="1"/>
+      <c r="C21" s="1"/>
+      <c r="D21" s="1"/>
+      <c r="E21" s="1"/>
+      <c r="F21" s="1"/>
+      <c r="G21" s="1"/>
+      <c r="H21" s="1"/>
+    </row>
+    <row r="22" spans="1:8">
+      <c r="A22" s="1"/>
+      <c r="B22" s="1"/>
+      <c r="C22" s="1"/>
+      <c r="D22" s="1"/>
+      <c r="E22" s="1"/>
+      <c r="F22" s="1"/>
+      <c r="G22" s="1"/>
+      <c r="H22" s="1"/>
+    </row>
+    <row r="23" spans="1:8">
       <c r="A23" s="1"/>
       <c r="B23" s="1"/>
       <c r="C23" s="1"/>
       <c r="D23" s="1"/>
-      <c r="E23" s="1"/>
+      <c r="E23" s="2"/>
       <c r="F23" s="1"/>
       <c r="G23" s="1"/>
       <c r="H23" s="1"/>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:8">
       <c r="A24" s="1"/>
       <c r="B24" s="1"/>
       <c r="C24" s="1"/>
-      <c r="D24" s="1"/>
+      <c r="D24" s="2"/>
       <c r="E24" s="2"/>
       <c r="F24" s="1"/>
       <c r="G24" s="1"/>
       <c r="H24" s="1"/>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:8">
       <c r="A25" s="1"/>
       <c r="B25" s="1"/>
       <c r="C25" s="1"/>
-      <c r="D25" s="2"/>
+      <c r="D25" s="1"/>
       <c r="E25" s="2"/>
       <c r="F25" s="1"/>
       <c r="G25" s="1"/>
       <c r="H25" s="1"/>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:8">
       <c r="A26" s="1"/>
       <c r="B26" s="1"/>
       <c r="C26" s="1"/>
@@ -1806,7 +1750,7 @@
       <c r="G26" s="1"/>
       <c r="H26" s="1"/>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:8">
       <c r="A27" s="1"/>
       <c r="B27" s="1"/>
       <c r="C27" s="1"/>
@@ -1816,7 +1760,7 @@
       <c r="G27" s="1"/>
       <c r="H27" s="1"/>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:8">
       <c r="A28" s="1"/>
       <c r="B28" s="1"/>
       <c r="C28" s="1"/>
@@ -1826,7 +1770,7 @@
       <c r="G28" s="1"/>
       <c r="H28" s="1"/>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:8">
       <c r="A29" s="1"/>
       <c r="B29" s="1"/>
       <c r="C29" s="1"/>
@@ -1836,7 +1780,7 @@
       <c r="G29" s="1"/>
       <c r="H29" s="1"/>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:8">
       <c r="A30" s="1"/>
       <c r="B30" s="1"/>
       <c r="C30" s="1"/>
@@ -1846,7 +1790,7 @@
       <c r="G30" s="1"/>
       <c r="H30" s="1"/>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:8">
       <c r="A31" s="1"/>
       <c r="B31" s="1"/>
       <c r="C31" s="1"/>
@@ -1856,7 +1800,7 @@
       <c r="G31" s="1"/>
       <c r="H31" s="1"/>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:8">
       <c r="A32" s="1"/>
       <c r="B32" s="1"/>
       <c r="C32" s="1"/>
@@ -1866,7 +1810,7 @@
       <c r="G32" s="1"/>
       <c r="H32" s="1"/>
     </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:8">
       <c r="A33" s="1"/>
       <c r="B33" s="1"/>
       <c r="C33" s="1"/>
@@ -1876,7 +1820,7 @@
       <c r="G33" s="1"/>
       <c r="H33" s="1"/>
     </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:8">
       <c r="A34" s="1"/>
       <c r="B34" s="1"/>
       <c r="C34" s="1"/>
@@ -1886,7 +1830,7 @@
       <c r="G34" s="1"/>
       <c r="H34" s="1"/>
     </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:8">
       <c r="A35" s="1"/>
       <c r="B35" s="1"/>
       <c r="C35" s="1"/>
@@ -1896,7 +1840,7 @@
       <c r="G35" s="1"/>
       <c r="H35" s="1"/>
     </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:8">
       <c r="A36" s="1"/>
       <c r="B36" s="1"/>
       <c r="C36" s="1"/>
@@ -1906,7 +1850,7 @@
       <c r="G36" s="1"/>
       <c r="H36" s="1"/>
     </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:8">
       <c r="A37" s="1"/>
       <c r="B37" s="1"/>
       <c r="C37" s="1"/>
@@ -1916,7 +1860,7 @@
       <c r="G37" s="1"/>
       <c r="H37" s="1"/>
     </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:8">
       <c r="A38" s="1"/>
       <c r="B38" s="1"/>
       <c r="C38" s="1"/>
@@ -1926,25 +1870,15 @@
       <c r="G38" s="1"/>
       <c r="H38" s="1"/>
     </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:8">
       <c r="A39" s="1"/>
       <c r="B39" s="1"/>
       <c r="C39" s="1"/>
-      <c r="D39" s="1"/>
+      <c r="D39" s="2"/>
       <c r="E39" s="2"/>
       <c r="F39" s="1"/>
       <c r="G39" s="1"/>
       <c r="H39" s="1"/>
-    </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A40" s="1"/>
-      <c r="B40" s="1"/>
-      <c r="C40" s="1"/>
-      <c r="D40" s="2"/>
-      <c r="E40" s="2"/>
-      <c r="F40" s="1"/>
-      <c r="G40" s="1"/>
-      <c r="H40" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1953,13 +1887,13 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CF8CB368-1F4F-4C65-B86B-93EC676CB77B}">
-  <dimension ref="A1:G38"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:J38"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="5" max="5" width="16.7265625" customWidth="1"/>
+    <col min="5" max="5" width="16.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:10">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1970,7 +1904,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:10" ht="42.75">
       <c r="A2" s="1" t="s">
         <v>19</v>
       </c>
@@ -1978,7 +1912,7 @@
         <v>10.6515835159838</v>
       </c>
       <c r="C2" s="1">
-        <v>0.17294771128421699</v>
+        <v>0.13468054835968099</v>
       </c>
       <c r="F2">
         <v>894</v>
@@ -1986,8 +1920,9 @@
       <c r="G2">
         <v>456</v>
       </c>
-    </row>
-    <row r="3" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="J2" s="1"/>
+    </row>
+    <row r="3" spans="1:10" ht="42.75">
       <c r="A3" s="1" t="s">
         <v>20</v>
       </c>
@@ -1995,7 +1930,7 @@
         <v>10.663341069103801</v>
       </c>
       <c r="C3" s="1">
-        <v>0.175665485735155</v>
+        <v>0.13679830071593899</v>
       </c>
       <c r="E3" t="s">
         <v>1</v>
@@ -2006,10 +1941,11 @@
       </c>
       <c r="G3">
         <f>AVERAGE(C2:C33)</f>
-        <v>0.17431068826518553</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+        <v>0.13575513971007916</v>
+      </c>
+      <c r="J3" s="1"/>
+    </row>
+    <row r="4" spans="1:10" ht="42.75">
       <c r="A4" s="1" t="s">
         <v>11</v>
       </c>
@@ -2017,7 +1953,7 @@
         <v>10.720671290806401</v>
       </c>
       <c r="C4" s="1">
-        <v>0.17382778027635701</v>
+        <v>0.135403359867214</v>
       </c>
       <c r="E4" t="s">
         <v>2</v>
@@ -2028,10 +1964,11 @@
       </c>
       <c r="G4">
         <f>_xlfn.STDEV.S(C2:C33)</f>
-        <v>1.6587992824535032E-3</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+        <v>1.2748321606246011E-3</v>
+      </c>
+      <c r="J4" s="1"/>
+    </row>
+    <row r="5" spans="1:10" ht="42.75">
       <c r="A5" s="1" t="s">
         <v>12</v>
       </c>
@@ -2039,7 +1976,7 @@
         <v>10.6070403098376</v>
       </c>
       <c r="C5" s="1">
-        <v>0.17455983570099701</v>
+        <v>0.13595989010586099</v>
       </c>
       <c r="E5" t="s">
         <v>3</v>
@@ -2050,10 +1987,11 @@
       </c>
       <c r="G5">
         <f>G4/G3/SQRT(COUNT(C2:C33))</f>
-        <v>2.1831974763881334E-3</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+        <v>2.1543681978898402E-3</v>
+      </c>
+      <c r="J5" s="1"/>
+    </row>
+    <row r="6" spans="1:10" ht="42.75">
       <c r="A6" s="1" t="s">
         <v>13</v>
       </c>
@@ -2061,10 +1999,11 @@
         <v>10.607916558495299</v>
       </c>
       <c r="C6" s="1">
-        <v>0.17664296551393399</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+        <v>0.13748020113746301</v>
+      </c>
+      <c r="J6" s="1"/>
+    </row>
+    <row r="7" spans="1:10" ht="42.75">
       <c r="A7" s="1" t="s">
         <v>14</v>
       </c>
@@ -2072,10 +2011,11 @@
         <v>10.796548325563</v>
       </c>
       <c r="C7" s="1">
-        <v>0.17708531560420199</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+        <v>0.13777383840185101</v>
+      </c>
+      <c r="J7" s="1"/>
+    </row>
+    <row r="8" spans="1:10" ht="42.75">
       <c r="A8" s="1" t="s">
         <v>15</v>
       </c>
@@ -2083,10 +2023,11 @@
         <v>10.8409786177823</v>
       </c>
       <c r="C8" s="1">
-        <v>0.17557573140333699</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+        <v>0.13676101673190699</v>
+      </c>
+      <c r="J8" s="1"/>
+    </row>
+    <row r="9" spans="1:10" ht="42.75">
       <c r="A9" s="1" t="s">
         <v>16</v>
       </c>
@@ -2094,10 +2035,11 @@
         <v>10.772956842649499</v>
       </c>
       <c r="C9" s="1">
-        <v>0.173457649972002</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+        <v>0.13512046849112699</v>
+      </c>
+      <c r="J9" s="1"/>
+    </row>
+    <row r="10" spans="1:10" ht="42.75">
       <c r="A10" s="1" t="s">
         <v>17</v>
       </c>
@@ -2105,10 +2047,11 @@
         <v>10.6830303352735</v>
       </c>
       <c r="C10" s="1">
-        <v>0.17535865105134299</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+        <v>0.13660109283925101</v>
+      </c>
+      <c r="J10" s="1"/>
+    </row>
+    <row r="11" spans="1:10" ht="42.75">
       <c r="A11" s="1" t="s">
         <v>18</v>
       </c>
@@ -2116,10 +2059,11 @@
         <v>10.585364148466899</v>
       </c>
       <c r="C11" s="1">
-        <v>0.175039518424147</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+        <v>0.13641311645492901</v>
+      </c>
+      <c r="J11" s="1"/>
+    </row>
+    <row r="12" spans="1:10" ht="42.75">
       <c r="A12" s="1" t="s">
         <v>24</v>
       </c>
@@ -2127,10 +2071,11 @@
         <v>10.5286364956397</v>
       </c>
       <c r="C12" s="1">
-        <v>0.17459939950666101</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+        <v>0.13599421764432501</v>
+      </c>
+      <c r="J12" s="1"/>
+    </row>
+    <row r="13" spans="1:10" ht="42.75">
       <c r="A13" s="1" t="s">
         <v>25</v>
       </c>
@@ -2138,10 +2083,11 @@
         <v>10.6204309820713</v>
       </c>
       <c r="C13" s="1">
-        <v>0.17177387798819599</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+        <v>0.133813897334362</v>
+      </c>
+      <c r="J13" s="1"/>
+    </row>
+    <row r="14" spans="1:10" ht="42.75">
       <c r="A14" s="1" t="s">
         <v>26</v>
       </c>
@@ -2149,10 +2095,11 @@
         <v>10.6162779389606</v>
       </c>
       <c r="C14" s="1">
-        <v>0.172049396498035</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+        <v>0.13398818137368401</v>
+      </c>
+      <c r="J14" s="1"/>
+    </row>
+    <row r="15" spans="1:10" ht="42.75">
       <c r="A15" s="1" t="s">
         <v>27</v>
       </c>
@@ -2160,10 +2107,11 @@
         <v>10.775713711424901</v>
       </c>
       <c r="C15" s="1">
-        <v>0.17416028353340501</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+        <v>0.135526162232535</v>
+      </c>
+      <c r="J15" s="1"/>
+    </row>
+    <row r="16" spans="1:10" ht="42.75">
       <c r="A16" s="1" t="s">
         <v>28</v>
       </c>
@@ -2171,10 +2119,11 @@
         <v>10.7723544954987</v>
       </c>
       <c r="C16" s="1">
-        <v>0.17432866559164001</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+        <v>0.13583799718759201</v>
+      </c>
+      <c r="J16" s="1"/>
+    </row>
+    <row r="17" spans="1:10" ht="42.75">
       <c r="A17" s="1" t="s">
         <v>29</v>
       </c>
@@ -2182,10 +2131,11 @@
         <v>10.7080767594852</v>
       </c>
       <c r="C17" s="1">
-        <v>0.17371638201273101</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+        <v>0.13529790524896701</v>
+      </c>
+      <c r="J17" s="1"/>
+    </row>
+    <row r="18" spans="1:10" ht="42.75">
       <c r="A18" s="1" t="s">
         <v>21</v>
       </c>
@@ -2193,10 +2143,11 @@
         <v>10.6292015876151</v>
       </c>
       <c r="C18" s="1">
-        <v>0.17123203171632401</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+        <v>0.13334859062780199</v>
+      </c>
+      <c r="J18" s="1"/>
+    </row>
+    <row r="19" spans="1:10" ht="42.75">
       <c r="A19" s="1" t="s">
         <v>22</v>
       </c>
@@ -2204,10 +2155,11 @@
         <v>10.6922490647235</v>
       </c>
       <c r="C19" s="1">
-        <v>0.17318569822136001</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+        <v>0.13491725008311001</v>
+      </c>
+      <c r="J19" s="1"/>
+    </row>
+    <row r="20" spans="1:10" ht="42.75">
       <c r="A20" s="1" t="s">
         <v>23</v>
       </c>
@@ -2215,87 +2167,88 @@
         <v>10.661460418557301</v>
       </c>
       <c r="C20" s="1">
-        <v>0.17669669700448201</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
+        <v>0.137631619653904</v>
+      </c>
+      <c r="J20" s="1"/>
+    </row>
+    <row r="21" spans="1:10">
       <c r="A21" s="1"/>
       <c r="B21" s="1"/>
       <c r="C21" s="1"/>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:10">
       <c r="A22" s="1"/>
       <c r="B22" s="1"/>
       <c r="C22" s="1"/>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:10">
       <c r="A23" s="1"/>
       <c r="B23" s="1"/>
       <c r="C23" s="1"/>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:10">
       <c r="A24" s="1"/>
       <c r="B24" s="1"/>
       <c r="C24" s="1"/>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:10">
       <c r="A25" s="1"/>
       <c r="B25" s="1"/>
       <c r="C25" s="1"/>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:10">
       <c r="A26" s="1"/>
       <c r="B26" s="1"/>
       <c r="C26" s="1"/>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:10">
       <c r="A27" s="1"/>
       <c r="B27" s="1"/>
       <c r="C27" s="1"/>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:10">
       <c r="A28" s="1"/>
       <c r="B28" s="1"/>
       <c r="C28" s="1"/>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:10">
       <c r="A29" s="1"/>
       <c r="B29" s="1"/>
       <c r="C29" s="1"/>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:10">
       <c r="A30" s="1"/>
       <c r="B30" s="1"/>
       <c r="C30" s="1"/>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:10">
       <c r="A31" s="1"/>
       <c r="B31" s="1"/>
       <c r="C31" s="1"/>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:10">
       <c r="A32" s="1"/>
       <c r="B32" s="1"/>
       <c r="C32" s="1"/>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:3">
       <c r="A33" s="1"/>
       <c r="B33" s="1"/>
       <c r="C33" s="1"/>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:3">
       <c r="C34" s="1"/>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:3">
       <c r="C35" s="1"/>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:3">
       <c r="C36" s="1"/>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:3">
       <c r="C37" s="1"/>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:3">
       <c r="C38" s="1"/>
     </row>
   </sheetData>
